--- a/UCAS mentor form.xlsx
+++ b/UCAS mentor form.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/hm1425_ic_ac_uk/Documents/STEMM/Term 1/UCAS mentoring testing/Matching Algorithm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C60F93E-AE8E-4E2B-8DAA-FC369904071C}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73FDADEC-5066-4A47-A1C5-0AD3B9F97671}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="24192" yWindow="2880" windowWidth="21600" windowHeight="11832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="30">
   <si>
     <t>ID</t>
   </si>
@@ -103,6 +103,18 @@
   </si>
   <si>
     <t>Max Mentees</t>
+  </si>
+  <si>
+    <t>5@5</t>
+  </si>
+  <si>
+    <t>6@6</t>
+  </si>
+  <si>
+    <t>7@7</t>
+  </si>
+  <si>
+    <t>8@8</t>
   </si>
 </sst>
 </file>
@@ -112,7 +124,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,6 +134,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -144,15 +164,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="10">
@@ -200,8 +224,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:K5" totalsRowShown="0">
-  <autoFilter ref="A1:K5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:K10" totalsRowShown="0">
+  <autoFilter ref="A1:K10" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time" dataDxfId="8"/>
@@ -516,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="9" width="20" bestFit="1" customWidth="1"/>
@@ -561,12 +585,7 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1">
-        <v>46263.819039351853</v>
-      </c>
+      <c r="B2" s="1"/>
       <c r="C2" s="1">
         <v>46263.819166666668</v>
       </c>
@@ -581,7 +600,7 @@
         <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J2">
         <v>2</v>
@@ -592,100 +611,261 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1">
-        <v>46263.819178240738</v>
+        <v>46263.819039351853</v>
       </c>
       <c r="C3" s="1">
-        <v>46263.819247685184</v>
+        <v>46263.819166666668</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="1">
-        <v>46263.81925925926</v>
+        <v>46263.819178240738</v>
       </c>
       <c r="C4" s="1">
-        <v>46263.819305555553</v>
+        <v>46263.819247685184</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1">
-        <v>46263.819328703707</v>
+        <v>46263.81925925926</v>
       </c>
       <c r="C5" s="1">
-        <v>46263.819374999999</v>
+        <v>46263.819305555553</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1">
+        <v>46263.819328703707</v>
+      </c>
+      <c r="C6" s="1">
+        <v>46263.819374999999</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H6" t="s">
         <v>23</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I6" t="s">
         <v>17</v>
       </c>
-      <c r="J5">
+      <c r="J6">
         <v>2</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1">
+        <v>46263.819039351853</v>
+      </c>
+      <c r="C7" s="1">
+        <v>46263.819166666668</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="3">
+        <v>5</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1">
+        <v>46263.819178240738</v>
+      </c>
+      <c r="C8" s="1">
+        <v>46263.819247685184</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="3">
+        <v>6</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1">
+        <v>46263.81925925926</v>
+      </c>
+      <c r="C9" s="1">
+        <v>46263.819305555553</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="3">
+        <v>7</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1">
+        <v>46263.819328703707</v>
+      </c>
+      <c r="C10" s="1">
+        <v>46263.819374999999</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="3">
+        <v>8</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10">
+        <v>3</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="H7" r:id="rId1" xr:uid="{B6238A33-C2E4-4524-AEA1-3C2A6ED61696}"/>
+    <hyperlink ref="H8" r:id="rId2" xr:uid="{0245BE31-D2AA-4055-A96D-C80B49D1BEA9}"/>
+    <hyperlink ref="H9:H10" r:id="rId3" display="6@6" xr:uid="{C3D6111D-B2B4-4A7A-9D40-81BBF7B60806}"/>
+    <hyperlink ref="H9" r:id="rId4" xr:uid="{A8101850-DA82-497F-9202-37D483EAA379}"/>
+    <hyperlink ref="H10" r:id="rId5" xr:uid="{416F854B-506A-4E4B-B602-F5E20F42081F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>